--- a/excel/铜.xlsx
+++ b/excel/铜.xlsx
@@ -1019,10 +1019,8 @@
         <f>IF(AND(ISNUMBER(T6),ISNUMBER(N6),N6&lt;&gt;0),(T6-N6)/N6,"-")</f>
         <v/>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>待发布(~8月中下旬)</t>
-        </is>
+      <c r="V6" t="n">
+        <v>175</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1031,7 +1029,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26Q1 +4%:波兰本部+8%(22Q1以来最高),International -31%(Robinson低品位);H1较预算低2%;6月单月59.3</t>
+          <t>26Q2=175kt（H1应付铜351kt +2%，减Q1 176kt推算）；波兰本部+International口径</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1728,16 +1726,14 @@
         <v/>
       </c>
       <c r="T13" t="n">
-        <v>96.5</v>
+        <v>96.46899999999999</v>
       </c>
       <c r="U13">
         <f>IF(AND(ISNUMBER(T13),ISNUMBER(N13),N13&lt;&gt;0),(T13-N13)/N13,"-")</f>
         <v/>
       </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>待发布(7/28盘后)</t>
-        </is>
+      <c r="V13" t="n">
+        <v>100.487</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1746,7 +1742,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Cobre Panama堆存矿处理获批(2026贡献30-40kt,累计约70kt至2027);Q1净亏$196M(品位下降+套保亏损+克瓦查升值)</t>
+          <t>2Q26：总铜100.5kt(+10.4% YoY)，Sentinel 50.3kt/Kansanshi 44.0kt/Cobre Panamá堆存处理3.2kt；来源：FQ 2Q26 报告(GlobeNewswire 2026-07-28)</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2021,10 +2017,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O16" t="n">
+        <v>59</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -2045,24 +2039,25 @@
         <f>IF(AND(ISNUMBER(R16),ISNUMBER(M16),M16&lt;&gt;0),(R16-M16)/M16,"-")</f>
         <v/>
       </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T16" t="n">
+        <v>49</v>
       </c>
       <c r="U16">
         <f>IF(AND(ISNUMBER(T16),ISNUMBER(N16),N16&lt;&gt;0),(T16-N16)/N16,"-")</f>
         <v/>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V16" t="n">
+        <v>56</v>
       </c>
       <c r="W16">
         <f>IF(AND(ISNUMBER(V16),ISNUMBER(O16),O16&lt;&gt;0),(V16-O16)/O16,"-")</f>
         <v/>
       </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>26Q2 铜 56kt（环比+14%/同比-5%，符合计划）；权益口径；FY26 指引 190-220kt 维持。源：Barrick Q2 2026 业绩（2026-08-10 官网）</t>
+        </is>
+      </c>
       <c r="Z16" t="inlineStr">
         <is>
           <t>黄金为主业，铜为板块口径（可回收磅，1M lbs=0.4536kt）；季报≈季后4-5周；2026-08-18新增骨架行，数据待回填</t>
@@ -2164,24 +2159,25 @@
         <f>IF(AND(ISNUMBER(R17),ISNUMBER(M17),M17&lt;&gt;0),(R17-M17)/M17,"-")</f>
         <v/>
       </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T17" t="n">
+        <v>47.96</v>
       </c>
       <c r="U17">
         <f>IF(AND(ISNUMBER(T17),ISNUMBER(N17),N17&lt;&gt;0),(T17-N17)/N17,"-")</f>
         <v/>
       </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V17" t="n">
+        <v>51.8</v>
       </c>
       <c r="W17">
         <f>IF(AND(ISNUMBER(V17),ISNUMBER(O17),O17&lt;&gt;0),(V17-O17)/O17,"-")</f>
         <v/>
       </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>26Q2 合并铜 51.8kt（Q1 47.96kt，-11% vs 25Q1 53.8kt 系 Mantoverde 罢工）；官方为 100% 合并口径（行标注 70% 权益口径勿混）；C1 $1.97/lb 纪录低位。源：Capstone Q1(4/29)/Q2(7/30) 2026 业绩</t>
+        </is>
+      </c>
       <c r="Z17" t="inlineStr">
         <is>
           <t>合并口径；季报≈季后4周；2026-08-18新增骨架行，数据待回填</t>
@@ -2259,10 +2255,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O18" t="n">
+        <v>29.228</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -2283,24 +2277,25 @@
         <f>IF(AND(ISNUMBER(R18),ISNUMBER(M18),M18&lt;&gt;0),(R18-M18)/M18,"-")</f>
         <v/>
       </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T18" t="n">
+        <v>22.868</v>
       </c>
       <c r="U18">
         <f>IF(AND(ISNUMBER(T18),ISNUMBER(N18),N18&lt;&gt;0),(T18-N18)/N18,"-")</f>
         <v/>
       </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V18" t="n">
+        <v>34.224</v>
       </c>
       <c r="W18">
         <f>IF(AND(ISNUMBER(V18),ISNUMBER(O18),O18&lt;&gt;0),(V18-O18)/O18,"-")</f>
         <v/>
       </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>26Q2=FY26Q4 铜 34.224kt（环比+50%：MATSA 16.219+Motheo 18.005，Motheo CuEq +65% 恢复）；FY26 铜 105.7kt；财年止 6 月已做日历映射。源：Sandfire 2026 年 6 月季报（7/23 ASX）</t>
+        </is>
+      </c>
       <c r="Z18" t="inlineStr">
         <is>
           <t>季报≈季后4周（ASX）；2026-08-18新增骨架行，数据待回填</t>
@@ -2378,10 +2373,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O19" t="n">
+        <v>44.356</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -2402,24 +2395,25 @@
         <f>IF(AND(ISNUMBER(R19),ISNUMBER(M19),M19&lt;&gt;0),(R19-M19)/M19,"-")</f>
         <v/>
       </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T19" t="n">
+        <v>24.514</v>
       </c>
       <c r="U19">
         <f>IF(AND(ISNUMBER(T19),ISNUMBER(N19),N19&lt;&gt;0),(T19-N19)/N19,"-")</f>
         <v/>
       </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V19" t="n">
+        <v>25.474</v>
       </c>
       <c r="W19">
         <f>IF(AND(ISNUMBER(V19),ISNUMBER(O19),O19&lt;&gt;0),(V19-O19)/O19,"-")</f>
         <v/>
       </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Kamoa-Kakula 100% 口径 26Q2=64,328t（阳极/ blister/渣精矿新口径；LCS 停产 56 天）；权益 39.6% 折算 25.47kt。注意：2025 列=精矿含铜旧口径（25Q2 112,009t→44.36kt）、26Q1=61,906t 精矿口径→24.51kt，口径切换不可直接同比。H2 爬产：Kamoa 采矿率+30% 至 8.5Mtpa；FY26 指引 290-330kt（100%）。源：Ivanhoe Q2 2026 产量公告（7/8）</t>
+        </is>
+      </c>
       <c r="Z19" t="inlineStr">
         <is>
           <t>跨品种修正：已在锌目录（Kipushi锌）；铜=Kamoa-Kakula；产量先行（季后1周）；2026-08-18新增骨架行，数据待回填</t>
@@ -2530,15 +2524,18 @@
         <f>IF(AND(ISNUMBER(T20),ISNUMBER(N20),N20&lt;&gt;0),(T20-N20)/N20,"-")</f>
         <v/>
       </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V20" t="n">
+        <v>54</v>
       </c>
       <c r="W20">
         <f>IF(AND(ISNUMBER(V20),ISNUMBER(O20),O20&lt;&gt;0),(V20-O20)/O20,"-")</f>
         <v/>
       </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>26Q2 合并（100%）铜 76.877kt；按行口径权益折算≈54.0kt（Caserones 34×51%+Candelaria 31×80%+Chapada ~11.9×100%）。Caserones 下调至指引下半区（天气）。源：Lundin Q2 2026 业绩（8/6）</t>
+        </is>
+      </c>
       <c r="Z20" t="inlineStr">
         <is>
           <t>跨品种修正：锌目录为占位行（锌资产2025-04-16售予Boliden）；铜为主业；季报≈季后4周；2026-08-18新增骨架行，数据待回填</t>
@@ -2616,10 +2613,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O21" t="n">
+        <v>29.956</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -2640,24 +2635,25 @@
         <f>IF(AND(ISNUMBER(R21),ISNUMBER(M21),M21&lt;&gt;0),(R21-M21)/M21,"-")</f>
         <v/>
       </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T21" t="n">
+        <v>27.929</v>
       </c>
       <c r="U21">
         <f>IF(AND(ISNUMBER(T21),ISNUMBER(N21),N21&lt;&gt;0),(T21-N21)/N21,"-")</f>
         <v/>
       </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V21" t="n">
+        <v>28.267</v>
       </c>
       <c r="W21">
         <f>IF(AND(ISNUMBER(V21),ISNUMBER(O21),O21&lt;&gt;0),(V21-O21)/O21,"-")</f>
         <v/>
       </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>26Q2 铜 28.267kt（环比+1.2%：BC 第二台 SAG 达产抵消秘鲁半年检修+港口延误 ~1 万 dmt 精矿延至 7 月）；FY26 指引 110-138kt 重申，现金成本指引下修。源：Hudbay Q2 2026 业绩（7/29）</t>
+        </is>
+      </c>
       <c r="Z21" t="inlineStr">
         <is>
           <t>跨品种修正：已在锌目录（Manitoba Lalor锌）；铜为主业；季报≈季后3-4周；2026-08-18新增骨架行，数据待回填</t>
@@ -2764,7 +2760,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
@@ -3008,10 +3003,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>待发布(中报~8月下旬)</t>
-        </is>
+      <c r="V2" t="n">
+        <v>27.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -3020,7 +3013,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26Q1 -9.9%:卡莫阿-卡库拉减产拖累(2025矿震涌水延续);巨龙二期2026/1投产Q1已贡献6万吨(达产30-35万吨/年)</t>
+          <t>中报（8/21）：H1 矿产铜 53.4 万吨（同比-5.7%，剔除卡莫阿影响 +5%）；26Q2=H1−Q1=27.5 万吨（推算，H1 减 Q1 25.9）。卡莫阿全年计划下调至 29-33 万吨。源：紫金矿业 2026 半年报</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -3116,10 +3109,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>待发布(中报~8月下旬)</t>
-        </is>
+      <c r="V3" t="n">
+        <v>20.01</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -3128,7 +3119,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26Q1 +10.15%:TFM技改2025完成2026满产+KFM放量;KFM二期2027投产(+10万吨/年)</t>
+          <t>中报（8/19）：H1 铜 38.7961 万吨（+9.73%）；26Q2=H1−Q1=20.01 万吨（推算），单季首破 20 万吨；TFM/KFM 稳定生产。源：洛阳钼业 2026 半年报</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -3338,20 +3329,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>未披露</t>
-        </is>
+      <c r="T5" t="n">
+        <v>63.02</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>待发布(中报~8月底)</t>
-        </is>
+      <c r="V5" t="n">
+        <v>63.02</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -3370,7 +3357,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>阴极铜:2023=209.73/2024=229.19/2025=238.04;仅年报/中报披露(23H1=98.83/24H1=117.50),季度由平台按年度均摊拟合(斜体);自产铜精矿含铜2023=20.20/2024=19.97/2025=26.99万吨(+35%)</t>
+          <t>阴极铜:2023=209.73/2024=229.19/2025=238.04;仅年报/中报披露(23H1=98.83/24H1=117.50),季度由平台按年度均摊拟合(斜体);自产铜精矿含铜2023=20.20/2024=19.97/2025=26.99万吨(+35%)；2026中报(8/25)：H1阴极铜126.04万吨(+5.44%)，Q1未披露，两季平分拟合；另自产铜精矿含铜13.64万吨(+37.36%)</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3463,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>待发布(中报~8月下旬)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -3496,7 +3483,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>阴极铜:2023=175.63/2024=176.80/2025=195.48;中报未披露产量明细,季度由平台均摊拟合(斜体);自产铜精矿2023=17.51(米拉多2023/9并表)/2024=15.52/2025=19.77万吨</t>
+          <t>阴极铜:2023=175.63/2024=176.80/2025=195.48;中报未披露产量明细,季度由平台均摊拟合(斜体);自产铜精矿2023=17.51(米拉多2023/9并表)/2024=15.52/2025=19.77万吨；2026中报(8/28)已核全文：仅财务+产能口径(阴极铜产能220万吨/年)，无产量吨数</t>
         </is>
       </c>
     </row>
@@ -3590,20 +3577,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>未披露</t>
-        </is>
+      <c r="T7" t="n">
+        <v>41.825</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>待发布(中报~8月下旬)</t>
-        </is>
+      <c r="V7" t="n">
+        <v>41.825</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -3622,7 +3605,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>阴极铜:2023=138.01/2024=120.60(西南铜业搬迁-12.6%)/2025=164.11(+36.1%,产能释放);仅年报/中报披露(23H1=65.87/24H1=50.87),季度平台拟合(斜体);自产铜精矿2023=6.37/2024=5.48/2025=6.94;凉山矿业12.5万吨2025/12/31投产试车(2026/3达产)</t>
+          <t>阴极铜:2023=138.01/2024=120.60(西南铜业搬迁-12.6%)/2025=164.11(+36.1%,产能释放);仅年报/中报披露(23H1=65.87/24H1=50.87),季度平台拟合(斜体);自产铜精矿2023=6.37/2024=5.48/2025=6.94;凉山矿业12.5万吨2025/12/31投产试车(2026/3达产)；2026中报(8/28)：H1阴极铜83.65万吨(合并口径)，Q1未披露，两季平分拟合；另精矿含铜3.37万吨</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3871,6 +3854,74 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>First Quantum 26Q1/26Q2 入库：96.5/100.5 kt（欠账补录，披露 7/28）</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>First Quantum 2Q26 Results (GlobeNewswire/EDGAR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>KGHM 铜 26Q2 补录 175kt（H1 351kt +2%，Q2=H1-Q1 推算）</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>来源：KGHM H1 2026 财报（handoff 已核）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>铜 26Q2 欠账补录：骨架 6 家（Barrick 56/Capstone 51.8/Sandfire 34.2/Ivanhoe 权益25.5/Lundin 权益~54/Hudbay 28.3 kt）+紫金 27.5/洛钼 20.01 万吨（中报 H1−Q1 推算）</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Barrick/Hudbay/Lundin/Ivanhoe/Capstone/Sandfire 官方 Q2 业绩；紫金/洛钼 2026 半年报</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>铜 26Q2 中报回填：江西铜业 H1=126.04→63.02/63.02、云南铜业 H1=83.65→41.825/41.825（平分拟合）；铜陵有色='-'（中报全文已核，无产量吨数）</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>江铜/云铜/铜陵 2026 中报（巨潮/新浪全文）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/excel/铜.xlsx
+++ b/excel/铜.xlsx
@@ -3727,7 +3727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3922,6 +3922,23 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>26Q2复核：铜陵有色——2026中报(8/28)复核确认无阴极铜产量吨数（仅产能220万吨/年+2026计划210.8万吨），维持"-"；集团口径H1阴极铜+16.96%为集团(非上市公司)口径不入库</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>铜陵有色2026半年度报告全文（新浪财经/巨潮）；国方数据中心8/1（集团口径）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
